--- a/diseases/d242/2000-2004.xlsx
+++ b/diseases/d242/2000-2004.xlsx
@@ -1086,6 +1086,2996 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_FI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Finland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_FI_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>27</v>
+      </c>
+      <c r="O6" t="n">
+        <v>27</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.04487288483970749</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>27</v>
+      </c>
+      <c r="O7" t="n">
+        <v>27</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_GB_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:GB:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>United Kingdom annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_GB_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — United Kingdom Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_HU_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:HU:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Hungary annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_HU_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Hungary Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>hpsc_ndh</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://notifiabledisease.hpsc.ie/</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>official_arcgis_feature_service</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>hpsc_ndh</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://notifiabledisease.hpsc.ie/</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>official_arcgis_feature_service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_IE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:IE:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Ireland annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_IE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>hpsc_ndh</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://notifiabledisease.hpsc.ie/</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_arcgis_feature_service</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>hpsc_ndh</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Ireland HPSC Notifiable Diseases Hub</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://notifiabledisease.hpsc.ie/</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_arcgis_feature_service</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_LV_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:LV:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Latvia annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_LV_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Latvia Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>76</v>
+      </c>
+      <c r="O14" t="n">
+        <v>76</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4626933544540673</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>76</v>
+      </c>
+      <c r="O15" t="n">
+        <v>76</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_NL_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:NL:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Netherlands annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_NL_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Netherlands Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>SER_NO_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>SRC_NO_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Norway annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_910_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lymphogranuloma-venereum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D242</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>性病性淋巴肉芽肿</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2004-01-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2004-01</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>SRC_SE_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Chlamydia infection, lymphogranuloma venereum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Sweden annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_SE_ECDC_LGV_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1202,7 +4192,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1212,7 +4202,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1232,7 +4222,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1242,7 +4232,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1264,7 +4254,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16">
